--- a/mrt/Singapore MRT gates.xlsx
+++ b/mrt/Singapore MRT gates.xlsx
@@ -16,1826 +16,1832 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="576">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Destination</t>
-  </si>
-  <si>
-    <t>Escalator(s)</t>
-  </si>
-  <si>
-    <t>TWD LINE</t>
-  </si>
-  <si>
-    <t>Stair(s)</t>
-  </si>
-  <si>
-    <t>Lift(s)</t>
-  </si>
-  <si>
-    <t>Pasir Ris</t>
-  </si>
-  <si>
-    <t>EW1  CR5  CP1</t>
-  </si>
-  <si>
-    <t>Pasir Ris / Changi Airport</t>
-  </si>
-  <si>
-    <t>7 18</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Tampines</t>
-  </si>
-  <si>
-    <t>EW2 – DT32</t>
-  </si>
-  <si>
-    <t>DT: 7</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Tuas Link</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Simei</t>
-  </si>
-  <si>
-    <t>EW3</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Tanah Merah</t>
-  </si>
-  <si>
-    <t>EW4  CG</t>
-  </si>
-  <si>
-    <t>Bedok</t>
-  </si>
-  <si>
-    <t>EW5</t>
-  </si>
-  <si>
-    <t>Kembangan</t>
-  </si>
-  <si>
-    <t>EW6</t>
-  </si>
-  <si>
-    <t>3 13</t>
-  </si>
-  <si>
-    <t>12 22</t>
-  </si>
-  <si>
-    <t>Eunos</t>
-  </si>
-  <si>
-    <t>EW7</t>
-  </si>
-  <si>
-    <t>8 19</t>
-  </si>
-  <si>
-    <t>6 17</t>
-  </si>
-  <si>
-    <t>Paya Lebar</t>
-  </si>
-  <si>
-    <t>EW8  CC9</t>
-  </si>
-  <si>
-    <t>7 12</t>
-  </si>
-  <si>
-    <t>CC: 24</t>
-  </si>
-  <si>
-    <t>7 12 24</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>13 18</t>
-  </si>
-  <si>
-    <t>CC: 1</t>
-  </si>
-  <si>
-    <t>1 13 18</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Aljunied</t>
-  </si>
-  <si>
-    <t>EW9</t>
-  </si>
-  <si>
-    <t>Kallang</t>
-  </si>
-  <si>
-    <t>EW10</t>
-  </si>
-  <si>
-    <t>Lavender</t>
-  </si>
-  <si>
-    <t>EW11</t>
-  </si>
-  <si>
-    <t>10 17</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>8 15</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Bugis</t>
-  </si>
-  <si>
-    <t>EW12  DT14</t>
-  </si>
-  <si>
-    <t>9 18</t>
-  </si>
-  <si>
-    <t>7 16</t>
-  </si>
-  <si>
-    <t>City Hall</t>
-  </si>
-  <si>
-    <t>EW13  NS25</t>
-  </si>
-  <si>
-    <t>9 20</t>
-  </si>
-  <si>
-    <t>TL/JE: 13 16</t>
-  </si>
-  <si>
-    <t>11 18</t>
-  </si>
-  <si>
-    <t>9 12</t>
-  </si>
-  <si>
-    <t>PR/MSP: 6 16</t>
-  </si>
-  <si>
-    <t>6 9 12 16</t>
-  </si>
-  <si>
-    <t>Raffles Place</t>
-  </si>
-  <si>
-    <t>EW14  NS26</t>
-  </si>
-  <si>
-    <t>6 19</t>
-  </si>
-  <si>
-    <t>TL/MSP: 9 16</t>
-  </si>
-  <si>
-    <t>11 14</t>
-  </si>
-  <si>
-    <t>10 15</t>
-  </si>
-  <si>
-    <t>PR/JE: 5 20</t>
-  </si>
-  <si>
-    <t>Tanjong Pagar</t>
-  </si>
-  <si>
-    <t>EW15</t>
-  </si>
-  <si>
-    <t>4 19✅</t>
-  </si>
-  <si>
-    <t>5✅ 21</t>
-  </si>
-  <si>
-    <t>17 10</t>
-  </si>
-  <si>
-    <t>Outram Park</t>
-  </si>
-  <si>
-    <t>EW16  NE3  TE17</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>7✅</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve"> 17</t>
-    </r>
-  </si>
-  <si>
-    <t>NE: 5 13
-TE: 7 17 21</t>
-  </si>
-  <si>
-    <t>5 10 15</t>
-  </si>
-  <si>
-    <t>7 18✅</t>
-  </si>
-  <si>
-    <t>NE: 12 20
-TE: 4 7 17</t>
-  </si>
-  <si>
-    <t>10 15 20</t>
-  </si>
-  <si>
-    <t>Tiong Bahru</t>
-  </si>
-  <si>
-    <t>EW17</t>
-  </si>
-  <si>
-    <t>10 21</t>
-  </si>
-  <si>
-    <t>4 15</t>
-  </si>
-  <si>
-    <t>Redhill</t>
-  </si>
-  <si>
-    <t>EW18</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Queenstown</t>
-  </si>
-  <si>
-    <t>EW19</t>
-  </si>
-  <si>
-    <t>14 18</t>
-  </si>
-  <si>
-    <t>7 11</t>
-  </si>
-  <si>
-    <t>Commonwealth</t>
-  </si>
-  <si>
-    <t>EW20</t>
-  </si>
-  <si>
-    <t>Buona Vista</t>
-  </si>
-  <si>
-    <t>EW21  CC22</t>
-  </si>
-  <si>
-    <t>14 5✅</t>
-  </si>
-  <si>
-    <t>CC: 5</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>11 19✅</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CC: </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>19</t>
-    </r>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Dover</t>
-  </si>
-  <si>
-    <t>EW22 Infill station</t>
-  </si>
-  <si>
-    <t>6 16</t>
-  </si>
-  <si>
-    <t>9 19</t>
-  </si>
-  <si>
-    <t>Clementi</t>
-  </si>
-  <si>
-    <t>EW23  CR17</t>
-  </si>
-  <si>
-    <t>Jurong East</t>
-  </si>
-  <si>
-    <t>EW24  NS1  JE5</t>
-  </si>
-  <si>
-    <t>8 18</t>
-  </si>
-  <si>
-    <t>7 17</t>
-  </si>
-  <si>
-    <t>Chinese Garden</t>
-  </si>
-  <si>
-    <t>EW25</t>
-  </si>
-  <si>
-    <t>Lakeside</t>
-  </si>
-  <si>
-    <t>EW26</t>
-  </si>
-  <si>
-    <t>Boon Lay</t>
-  </si>
-  <si>
-    <t>EW27  JS8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>5 16</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Pioneer</t>
-  </si>
-  <si>
-    <t>EW28</t>
-  </si>
-  <si>
-    <t>8 16</t>
-  </si>
-  <si>
-    <t>9 17</t>
-  </si>
-  <si>
-    <t>Joo Koon</t>
-  </si>
-  <si>
-    <t>EW29</t>
-  </si>
-  <si>
-    <t>8 17</t>
-  </si>
-  <si>
-    <t>Gul Circle</t>
-  </si>
-  <si>
-    <t>EW30</t>
-  </si>
-  <si>
-    <t>10 16 17</t>
-  </si>
-  <si>
-    <t>5 10 17 21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>13 20</t>
-  </si>
-  <si>
-    <t>7 24</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Tuas Crescent</t>
-  </si>
-  <si>
-    <t>EW31</t>
-  </si>
-  <si>
-    <t>3 14 18</t>
-  </si>
-  <si>
-    <t>6 23</t>
-  </si>
-  <si>
-    <t>7 11 22</t>
-  </si>
-  <si>
-    <t>2 19</t>
-  </si>
-  <si>
-    <t>Tuas West Road</t>
-  </si>
-  <si>
-    <t>EW32</t>
-  </si>
-  <si>
-    <t>4 14 18</t>
-  </si>
-  <si>
-    <t>9 21</t>
-  </si>
-  <si>
-    <t>7 11 21</t>
-  </si>
-  <si>
-    <t>4 16</t>
-  </si>
-  <si>
-    <t>Expo</t>
-  </si>
-  <si>
-    <t>CG1</t>
-  </si>
-  <si>
-    <t>5 13 21</t>
-  </si>
-  <si>
-    <t>DT: 13</t>
-  </si>
-  <si>
-    <t>13 21</t>
-  </si>
-  <si>
-    <t>1 7</t>
-  </si>
-  <si>
-    <t>Changi Airport</t>
-  </si>
-  <si>
-    <t>CG2</t>
-  </si>
-  <si>
-    <t>T1, T3, T4: 20
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="576">
+  <ns0:si>
+    <ns0:t>Name</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Code</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Destination</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Escalator(s)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TWD LINE</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Stair(s)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Lift(s)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Pasir Ris</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW1  CR5  CP1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Pasir Ris / Changi Airport</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tampines</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW2 – DT32</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT: 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tuas Link</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Simei</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tanah Merah</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW4  CG</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bedok</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kembangan</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12 22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Eunos</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Paya Lebar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW8  CC9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 12 24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 13 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Aljunied</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kallang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Lavender</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bugis</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW12  DT14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>City Hall</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW13  NS25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TL/JE: 13 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PR/MSP: 6 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 9 12 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Raffles Place</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW14  NS26</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TL/MSP: 9 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11 14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PR/JE: 5 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tanjong Pagar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 19✅</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5✅ 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Outram Park</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW16  NE3  TE17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:b/>
+        <ns0:color theme="1"/>
+      </ns0:rPr>
+      <ns0:t>7✅</ns0:t>
+    </ns0:r>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:color theme="1"/>
+      </ns0:rPr>
+      <ns0:t xml:space="preserve"> 17</ns0:t>
+    </ns0:r>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 5 13
+TE: 7 17 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 10 15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 18✅</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 12 20
+TE: 4 7 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 15 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tiong Bahru</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Redhill</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Queenstown</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Commonwealth</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Buona Vista</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW21  CC22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>14 5✅</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11 19✅</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:r>
+      <ns0:t xml:space="preserve">CC: </ns0:t>
+    </ns0:r>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:b/>
+        <ns0:color theme="1"/>
+      </ns0:rPr>
+      <ns0:t>19</ns0:t>
+    </ns0:r>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dover</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW22 Infill station</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Clementi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW23  CR17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Jurong East</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW24  NS1  JE5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Chinese Garden</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Lakeside</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW26</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Boon Lay</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW27  JS8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Pioneer</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW28</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Joo Koon</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW29</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Gul Circle</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW30</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 16 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 10 17 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tuas Crescent</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW31</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 14 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 11 22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tuas West Road</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW32</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 14 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 11 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Expo</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CG1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 13 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT: 13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Changi Airport</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CG2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>T1, T3, T4: 20
 T2: 5
-Jewel: 20</t>
-  </si>
-  <si>
-    <t>NS1  EW24  JE5</t>
-  </si>
-  <si>
-    <t>NS2</t>
-  </si>
-  <si>
-    <t>Bukit Batok</t>
-  </si>
-  <si>
-    <t>Marina South Pier</t>
-  </si>
-  <si>
-    <t>NS3</t>
-  </si>
-  <si>
-    <t>Bukit Gombak</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF000000"/>
-      </rPr>
-      <t xml:space="preserve">NS3A </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF000000"/>
-        <u/>
-      </rPr>
-      <t>Infill station</t>
-    </r>
-  </si>
-  <si>
-    <t>Brickland</t>
-  </si>
-  <si>
-    <t>NS4  BP1  JS1</t>
-  </si>
-  <si>
-    <t>Choa Chu Kang</t>
-  </si>
-  <si>
-    <t>6 8</t>
-  </si>
-  <si>
-    <t>17 19</t>
-  </si>
-  <si>
-    <t>NS5</t>
-  </si>
-  <si>
-    <t>Yew Tee</t>
-  </si>
-  <si>
-    <t>NS7</t>
-  </si>
-  <si>
-    <t>Kranji</t>
-  </si>
-  <si>
-    <t>NS8</t>
-  </si>
-  <si>
-    <t>Marsiling</t>
-  </si>
-  <si>
-    <t>NS9  TE2</t>
-  </si>
-  <si>
-    <t>Woodlands</t>
-  </si>
-  <si>
-    <t>TE: 23</t>
-  </si>
-  <si>
-    <t>TE: 2</t>
-  </si>
-  <si>
-    <t>NS10</t>
-  </si>
-  <si>
-    <t>Admiralty</t>
-  </si>
-  <si>
-    <t>NS11</t>
-  </si>
-  <si>
-    <t>Sembawang</t>
-  </si>
-  <si>
-    <t>NS12</t>
-  </si>
-  <si>
-    <t>Canberra</t>
-  </si>
-  <si>
-    <t>NS13</t>
-  </si>
-  <si>
-    <t>Yishun</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>NS14</t>
-  </si>
-  <si>
-    <t>Khatib</t>
-  </si>
-  <si>
-    <t>NS15</t>
-  </si>
-  <si>
-    <t>Yio Chu Kang</t>
-  </si>
-  <si>
-    <t>NS16  CR11</t>
-  </si>
-  <si>
-    <t>Ang Mo Kio</t>
-  </si>
-  <si>
-    <t>4 17</t>
-  </si>
-  <si>
-    <t>8 21</t>
-  </si>
-  <si>
-    <t>NS17  CC15</t>
-  </si>
-  <si>
-    <t>Bishan</t>
-  </si>
-  <si>
-    <t>8 9 16</t>
-  </si>
-  <si>
-    <t>5 9 16</t>
-  </si>
-  <si>
-    <t>CC: 17</t>
-  </si>
-  <si>
-    <t>9 16</t>
-  </si>
-  <si>
-    <t>9 11 16 22</t>
-  </si>
-  <si>
-    <t>CC: 22</t>
-  </si>
-  <si>
-    <t>NS18</t>
-  </si>
-  <si>
-    <t>Braddell</t>
-  </si>
-  <si>
-    <t>NS19</t>
-  </si>
-  <si>
-    <t>Toa Payoh</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>NS20</t>
-  </si>
-  <si>
-    <t>Novena</t>
-  </si>
-  <si>
-    <t>NS21 – DT11</t>
-  </si>
-  <si>
-    <t>Newton</t>
-  </si>
-  <si>
-    <t>NS22  TE14</t>
-  </si>
-  <si>
-    <t>Orchard</t>
-  </si>
-  <si>
-    <t>10 13</t>
-  </si>
-  <si>
-    <t>TE: 14 21</t>
-  </si>
-  <si>
-    <t>12 15</t>
-  </si>
-  <si>
-    <t>TE: 4 11</t>
-  </si>
-  <si>
-    <t>NS23</t>
-  </si>
-  <si>
-    <t>Somerset</t>
-  </si>
-  <si>
-    <t>8 12 15 19</t>
-  </si>
-  <si>
-    <t>6 10 13 17</t>
-  </si>
-  <si>
-    <t>NS24  NE6  CC1</t>
-  </si>
-  <si>
-    <t>Dhoby Ghaut</t>
-  </si>
-  <si>
-    <t>5 11 14 20</t>
-  </si>
-  <si>
-    <t>NE: 8 17</t>
-  </si>
-  <si>
-    <t>NS25  EW13</t>
-  </si>
-  <si>
-    <t>13 16</t>
-  </si>
-  <si>
-    <t>9 13 16 19</t>
-  </si>
-  <si>
-    <t>Thus Link/Marina South Pier: 9 19</t>
-  </si>
-  <si>
-    <t>7 14</t>
-  </si>
-  <si>
-    <t>Thus Link/Jurong East: 9 12</t>
-  </si>
-  <si>
-    <t>NS26  EW14</t>
-  </si>
-  <si>
-    <t>PR/MSP: 9 19</t>
-  </si>
-  <si>
-    <t>5 20</t>
-  </si>
-  <si>
-    <t>NS27  CE2  TE20</t>
-  </si>
-  <si>
-    <t>Marina Bay</t>
-  </si>
-  <si>
-    <t>NS28</t>
-  </si>
-  <si>
-    <t>6 13 19</t>
-  </si>
-  <si>
-    <t>NE1  CC29</t>
-  </si>
-  <si>
-    <t>HarbourFront</t>
-  </si>
-  <si>
-    <t>Harbourfront</t>
-  </si>
-  <si>
-    <t>NE3  EW16  TE17</t>
-  </si>
-  <si>
-    <t>11 13 19✅</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">11 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
-      </rPr>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
-      </rPr>
-      <t xml:space="preserve"> 19</t>
-    </r>
-  </si>
-  <si>
-    <t>EW: 13
-TE: 19</t>
-  </si>
-  <si>
-    <t>Punggol</t>
-  </si>
-  <si>
-    <t>12 14 19✅</t>
-  </si>
-  <si>
-    <t>6 12 14</t>
-  </si>
-  <si>
-    <t>EW: 12
-TE: 6</t>
-  </si>
-  <si>
-    <t>NE4  DT19</t>
-  </si>
-  <si>
-    <t>Chinatown</t>
-  </si>
-  <si>
-    <t>2 12 19</t>
-  </si>
-  <si>
-    <t>2 10</t>
-  </si>
-  <si>
-    <t>DT: 1</t>
-  </si>
-  <si>
-    <t>2 10 19</t>
-  </si>
-  <si>
-    <t>NE5</t>
-  </si>
-  <si>
-    <t>Clarke Quay</t>
-  </si>
-  <si>
-    <t>4 11 14 21</t>
-  </si>
-  <si>
-    <t>NE6  NS24  CC1</t>
-  </si>
-  <si>
-    <t>4 16 20</t>
-  </si>
-  <si>
-    <t>9 13 18</t>
-  </si>
-  <si>
-    <t>5 9 21</t>
-  </si>
-  <si>
-    <t>NS: 9</t>
-  </si>
-  <si>
-    <t>NE7  DT12</t>
-  </si>
-  <si>
-    <t>Little India</t>
-  </si>
-  <si>
-    <t>DT: 8</t>
-  </si>
-  <si>
-    <t>DT: 17</t>
-  </si>
-  <si>
-    <t>NE8</t>
-  </si>
-  <si>
-    <t>Farrer Park</t>
-  </si>
-  <si>
-    <t>City Square: 17</t>
-  </si>
-  <si>
-    <t>City Square: 8</t>
-  </si>
-  <si>
-    <t>NE9</t>
-  </si>
-  <si>
-    <t>Boon Keng</t>
-  </si>
-  <si>
-    <t>NE10</t>
-  </si>
-  <si>
-    <t>Potong Pasir</t>
-  </si>
-  <si>
-    <t>NE11</t>
-  </si>
-  <si>
-    <t>Woodleigh</t>
-  </si>
-  <si>
-    <t>NE12  CC13</t>
-  </si>
-  <si>
-    <t>Serangoon</t>
-  </si>
-  <si>
-    <t>6 19 29</t>
-  </si>
-  <si>
-    <t>CC: 9</t>
-  </si>
-  <si>
-    <t>5 6 19</t>
-  </si>
-  <si>
-    <t>CC: 16</t>
-  </si>
-  <si>
-    <t>NE13</t>
-  </si>
-  <si>
-    <t>Kovan</t>
-  </si>
-  <si>
-    <t>Heartland Mall: 17</t>
-  </si>
-  <si>
-    <t>Hertland Mall: 8</t>
-  </si>
-  <si>
-    <t>NE14  CR8</t>
-  </si>
-  <si>
-    <t>Hougang</t>
-  </si>
-  <si>
-    <t>Hougang Mall: 17</t>
-  </si>
-  <si>
-    <t>Hougang Mall: 8</t>
-  </si>
-  <si>
-    <t>NE15</t>
-  </si>
-  <si>
-    <t>Buangkok</t>
-  </si>
-  <si>
-    <t>9 16 24</t>
-  </si>
-  <si>
-    <t>NE16  STC</t>
-  </si>
-  <si>
-    <t>Sengkang</t>
-  </si>
-  <si>
-    <t>7 11 20</t>
-  </si>
-  <si>
-    <t>5 14 18</t>
-  </si>
-  <si>
-    <t>NE17  PTC  CP4</t>
-  </si>
-  <si>
-    <t>5 14 23</t>
-  </si>
-  <si>
-    <t>CC1  NS24  NE6</t>
-  </si>
-  <si>
-    <t>Marina Bay / Dhoby Ghaut</t>
-  </si>
-  <si>
-    <t>1 12</t>
-  </si>
-  <si>
-    <t>5 10</t>
-  </si>
-  <si>
-    <t>CC2</t>
-  </si>
-  <si>
-    <t>Bras Basah</t>
-  </si>
-  <si>
-    <t>3 10</t>
-  </si>
-  <si>
-    <t>CC3</t>
-  </si>
-  <si>
-    <t>Esplanade</t>
-  </si>
-  <si>
-    <t>2 11</t>
-  </si>
-  <si>
-    <t>CC4  DT15</t>
-  </si>
-  <si>
-    <t>Promenade</t>
-  </si>
-  <si>
-    <t>2 10 12</t>
-  </si>
-  <si>
-    <t>HF: 9
-DT: 7</t>
-  </si>
-  <si>
-    <t>1 11</t>
-  </si>
-  <si>
-    <t>DG/MSP: 8
-DT: 11</t>
-  </si>
-  <si>
-    <t>CC5</t>
-  </si>
-  <si>
-    <t>Nicoll Highway</t>
-  </si>
-  <si>
-    <t>CC6</t>
-  </si>
-  <si>
-    <t>Stadium</t>
-  </si>
-  <si>
-    <t>Kallang Leisure Park: 12</t>
-  </si>
-  <si>
-    <t>Kallang Leisure Park: 1</t>
-  </si>
-  <si>
-    <t>CC7</t>
-  </si>
-  <si>
-    <t>Mountbatten</t>
-  </si>
-  <si>
-    <t>CC8</t>
-  </si>
-  <si>
-    <t>Dakota</t>
-  </si>
-  <si>
-    <t>5 8</t>
-  </si>
-  <si>
-    <t>CC9  EW8</t>
-  </si>
-  <si>
-    <t>EW: 10</t>
-  </si>
-  <si>
-    <t>EW: 3</t>
-  </si>
-  <si>
-    <t>CC10  DT26</t>
-  </si>
-  <si>
-    <t>MacPherson</t>
-  </si>
-  <si>
-    <t>2 5 8 11</t>
-  </si>
-  <si>
-    <t>BP: 1
-Expo: 12</t>
-  </si>
-  <si>
-    <t>BP: 12
-Expo: 1</t>
-  </si>
-  <si>
-    <t>CC11</t>
-  </si>
-  <si>
-    <t>Tai Seng</t>
-  </si>
-  <si>
-    <t>5 7</t>
-  </si>
-  <si>
-    <t>CC12</t>
-  </si>
-  <si>
-    <t>Bartley</t>
-  </si>
-  <si>
-    <t>CC13  NE12</t>
-  </si>
-  <si>
-    <t>NE: 1
-Nex: 1</t>
-  </si>
-  <si>
-    <t>6 12</t>
-  </si>
-  <si>
-    <t>NE: 12
-Nex: 12</t>
-  </si>
-  <si>
-    <t>CC14</t>
-  </si>
-  <si>
-    <t>Lorong Chuan</t>
-  </si>
-  <si>
-    <t>CC15  NS17</t>
-  </si>
-  <si>
-    <t>5 12</t>
-  </si>
-  <si>
-    <t>NS: 12</t>
-  </si>
-  <si>
-    <t>1 8</t>
-  </si>
-  <si>
-    <t>NS: 1</t>
-  </si>
-  <si>
-    <t>CC16</t>
-  </si>
-  <si>
-    <t>Marymount</t>
-  </si>
-  <si>
-    <t>CC17  TE9</t>
-  </si>
-  <si>
-    <t>Caldecott</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>TE: 6</t>
-  </si>
-  <si>
-    <t>TE: 7</t>
-  </si>
-  <si>
-    <t>CC18  Infill station</t>
-  </si>
-  <si>
-    <t>Bukit Brown</t>
-  </si>
-  <si>
-    <t>CC19  DT9</t>
-  </si>
-  <si>
-    <t>Botanic Gardens</t>
-  </si>
-  <si>
-    <t>DT: 5</t>
-  </si>
-  <si>
-    <t>CC20</t>
-  </si>
-  <si>
-    <t>Farrer Road</t>
-  </si>
-  <si>
-    <t>CC21</t>
-  </si>
-  <si>
-    <t>Holland Village</t>
-  </si>
-  <si>
-    <t>CC22  EW21</t>
-  </si>
-  <si>
-    <t>5 8✅(出口)</t>
-  </si>
-  <si>
-    <t>5✅ 8</t>
-  </si>
-  <si>
-    <t>CC23</t>
-  </si>
-  <si>
-    <t>one-north</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1 5 8</t>
-  </si>
-  <si>
-    <t>5 8 12</t>
-  </si>
-  <si>
-    <t>CC24</t>
-  </si>
-  <si>
-    <t>Kent Ridge</t>
-  </si>
-  <si>
-    <t>CC25</t>
-  </si>
-  <si>
-    <t>Haw Par Villa</t>
-  </si>
-  <si>
-    <t>CC26</t>
-  </si>
-  <si>
-    <t>Pasir Panjang</t>
-  </si>
-  <si>
-    <t>CC27</t>
-  </si>
-  <si>
-    <t>Labrador Park</t>
-  </si>
-  <si>
-    <t>CC28</t>
-  </si>
-  <si>
-    <t>Telok Blangah</t>
-  </si>
-  <si>
-    <t>CC29  NE1</t>
-  </si>
-  <si>
-    <t>NE: 1</t>
-  </si>
-  <si>
-    <t>CE1</t>
-  </si>
-  <si>
-    <t>Bayfront</t>
-  </si>
-  <si>
-    <t>3 12</t>
-  </si>
-  <si>
-    <t>5 10 11</t>
-  </si>
-  <si>
-    <t>DG/MSP: 5
-MBS: 12</t>
-  </si>
-  <si>
-    <t>2 3</t>
-  </si>
-  <si>
-    <t>MSP: 4</t>
-  </si>
-  <si>
-    <t>CE2</t>
-  </si>
-  <si>
-    <t>DT1 – BP6</t>
-  </si>
-  <si>
-    <t>Bukit Panjang</t>
-  </si>
-  <si>
-    <t>DT2</t>
-  </si>
-  <si>
-    <t>Cashew</t>
-  </si>
-  <si>
-    <t>DT3</t>
-  </si>
-  <si>
-    <t>Hillview</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF000000"/>
-      </rPr>
-      <t xml:space="preserve">DT4 </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF000000"/>
-        <u/>
-      </rPr>
-      <t>Infill station</t>
-    </r>
-  </si>
-  <si>
-    <t>Hume</t>
-  </si>
-  <si>
-    <t>DT5</t>
-  </si>
-  <si>
-    <t>Beauty World</t>
-  </si>
-  <si>
-    <t>DT6  CR15</t>
-  </si>
-  <si>
-    <t>King Albert Park</t>
-  </si>
-  <si>
-    <t>DT7</t>
-  </si>
-  <si>
-    <t>Sixth Avenue</t>
-  </si>
-  <si>
-    <t>DT8</t>
-  </si>
-  <si>
-    <t>Tan Kah Kee</t>
-  </si>
-  <si>
-    <t>DT9  CC19</t>
-  </si>
-  <si>
-    <t>5 6</t>
-  </si>
-  <si>
-    <t>CC: 10</t>
-  </si>
-  <si>
-    <t>7 8</t>
-  </si>
-  <si>
-    <t>CC: 3</t>
-  </si>
-  <si>
-    <t>DT10  TE11</t>
-  </si>
-  <si>
-    <t>Stevens</t>
-  </si>
-  <si>
-    <t>DT11 – NS21</t>
-  </si>
-  <si>
-    <t>NS: 5</t>
-  </si>
-  <si>
-    <t>NS: 8</t>
-  </si>
-  <si>
-    <t>DT12  NE7</t>
-  </si>
-  <si>
-    <t>1 4</t>
-  </si>
-  <si>
-    <t>NE: 5</t>
-  </si>
-  <si>
-    <t>NE: 8</t>
-  </si>
-  <si>
-    <t>DT13</t>
-  </si>
-  <si>
-    <t>Rochor</t>
-  </si>
-  <si>
-    <t>DT14  EW12</t>
-  </si>
-  <si>
-    <t>EW: 6</t>
-  </si>
-  <si>
-    <t>EW: 7</t>
-  </si>
-  <si>
-    <t>DT15  CC4</t>
-  </si>
-  <si>
-    <t>CC: 6</t>
-  </si>
-  <si>
-    <t>CC: 7</t>
-  </si>
-  <si>
-    <t>DT16  CE1</t>
-  </si>
-  <si>
-    <t>Expo/MBS: 4</t>
-  </si>
-  <si>
-    <t>4 10</t>
-  </si>
-  <si>
-    <t>BP/HF: 5</t>
-  </si>
-  <si>
-    <t>DT17</t>
-  </si>
-  <si>
-    <t>Downtown</t>
-  </si>
-  <si>
-    <t>2 9</t>
-  </si>
-  <si>
-    <t>4 11</t>
-  </si>
-  <si>
-    <t>DT18</t>
-  </si>
-  <si>
-    <t>Telok Ayer</t>
-  </si>
-  <si>
-    <t>6 9</t>
-  </si>
-  <si>
-    <t>4 7</t>
-  </si>
-  <si>
-    <t>DT19  NE4</t>
-  </si>
-  <si>
-    <t>1 9 12</t>
-  </si>
-  <si>
-    <t>1 3</t>
-  </si>
-  <si>
-    <t>NE: 9 12</t>
-  </si>
-  <si>
-    <t>1 4 12</t>
-  </si>
-  <si>
-    <t>NE: 1 4</t>
-  </si>
-  <si>
-    <t>DT20</t>
-  </si>
-  <si>
-    <t>Fort Canning</t>
-  </si>
-  <si>
-    <t>DT21</t>
-  </si>
-  <si>
-    <t>Bencoolen</t>
-  </si>
-  <si>
-    <t>6 7</t>
-  </si>
-  <si>
-    <t>DT22</t>
-  </si>
-  <si>
-    <t>Jalan Besar</t>
-  </si>
-  <si>
-    <t>DT23</t>
-  </si>
-  <si>
-    <t>Bendemeer</t>
-  </si>
-  <si>
-    <t>DT24</t>
-  </si>
-  <si>
-    <t>Geylang Bahru</t>
-  </si>
-  <si>
-    <t>DT25</t>
-  </si>
-  <si>
-    <t>Mattar</t>
-  </si>
-  <si>
-    <t>DT26  CC10</t>
-  </si>
-  <si>
-    <t>Expo: 1
-CC: 9</t>
-  </si>
-  <si>
-    <t>BP: 12
-CC: 3</t>
-  </si>
-  <si>
-    <t>DT27</t>
-  </si>
-  <si>
-    <t>Ubi</t>
-  </si>
-  <si>
-    <t>8 10</t>
-  </si>
-  <si>
-    <t>3 6</t>
-  </si>
-  <si>
-    <t>DT28</t>
-  </si>
-  <si>
-    <t>Kaki Bukit</t>
-  </si>
-  <si>
-    <t>DT29</t>
-  </si>
-  <si>
-    <t>Bedok North</t>
-  </si>
-  <si>
-    <t>DT30</t>
-  </si>
-  <si>
-    <t>Bedok Reservoir</t>
-  </si>
-  <si>
-    <t>DT31</t>
-  </si>
-  <si>
-    <t>Tampines West</t>
-  </si>
-  <si>
-    <t>DT32 – EW2</t>
-  </si>
-  <si>
-    <t>EW: 8</t>
-  </si>
-  <si>
-    <t>EW: 5</t>
-  </si>
-  <si>
-    <t>DT33</t>
-  </si>
-  <si>
-    <t>Tampines East</t>
-  </si>
-  <si>
-    <t>DT34</t>
-  </si>
-  <si>
-    <t>Upper Changi</t>
-  </si>
-  <si>
-    <t>DT35  CG1</t>
-  </si>
-  <si>
-    <t>TE1 – RTS</t>
-  </si>
-  <si>
-    <t>Woodlands North</t>
-  </si>
-  <si>
-    <t>1 12 20</t>
-  </si>
-  <si>
-    <t>TE2  NS9</t>
-  </si>
-  <si>
-    <t>4 12 17</t>
-  </si>
-  <si>
-    <t>NS: 4</t>
-  </si>
-  <si>
-    <t>Gardens by the Bay</t>
-  </si>
-  <si>
-    <t>4 9 17</t>
-  </si>
-  <si>
-    <t>6 20</t>
-  </si>
-  <si>
-    <t>NS: 17</t>
-  </si>
-  <si>
-    <t>TE3</t>
-  </si>
-  <si>
-    <t>Woodlands South</t>
-  </si>
-  <si>
-    <t>8 13</t>
-  </si>
-  <si>
-    <t>TE4</t>
-  </si>
-  <si>
-    <t>Springleaf</t>
-  </si>
-  <si>
-    <t>8 12</t>
-  </si>
-  <si>
-    <t>10 11</t>
-  </si>
-  <si>
-    <t>TE5</t>
-  </si>
-  <si>
-    <t>Lentor</t>
-  </si>
-  <si>
-    <t>TE6</t>
-  </si>
-  <si>
-    <t>Mayflower</t>
-  </si>
-  <si>
-    <t>TE7  CR13</t>
-  </si>
-  <si>
-    <t>Bright Hill</t>
-  </si>
-  <si>
-    <t>1 8 12</t>
-  </si>
-  <si>
-    <t>1 10</t>
-  </si>
-  <si>
-    <t>9 13 20</t>
-  </si>
-  <si>
-    <t>11 20</t>
-  </si>
-  <si>
-    <t>9 13</t>
-  </si>
-  <si>
-    <t>TE8</t>
-  </si>
-  <si>
-    <t>Upper Thomson</t>
-  </si>
-  <si>
-    <t>TE9  CC17</t>
-  </si>
-  <si>
-    <t>CC: 2</t>
-  </si>
-  <si>
-    <t>CC: 19</t>
-  </si>
-  <si>
-    <t>TE11  DT10</t>
-  </si>
-  <si>
-    <t>4 13 17</t>
-  </si>
-  <si>
-    <t>1 7 13 17</t>
-  </si>
-  <si>
-    <t>BP: 13
-Expo: 4</t>
-  </si>
-  <si>
-    <t>4 8 17</t>
-  </si>
-  <si>
-    <t>15 16</t>
-  </si>
-  <si>
-    <t>4 8 14 20</t>
-  </si>
-  <si>
-    <t>BP: 8
-Expo: 17</t>
-  </si>
-  <si>
-    <t>TE12</t>
-  </si>
-  <si>
-    <t>Napier</t>
-  </si>
-  <si>
-    <t>1 8 13 20</t>
-  </si>
-  <si>
-    <t>GBTB: 8 13</t>
-  </si>
-  <si>
-    <t>5 9 12 16</t>
-  </si>
-  <si>
-    <t>WN: 9 12</t>
-  </si>
-  <si>
-    <t>TE13</t>
-  </si>
-  <si>
-    <t>Orchard Boulevard</t>
-  </si>
-  <si>
-    <t>3 18</t>
-  </si>
-  <si>
-    <t>TE14  NS22</t>
-  </si>
-  <si>
-    <t>3(NS→Exit 1) 9 12 18</t>
-  </si>
-  <si>
-    <t>3 9 18</t>
-  </si>
-  <si>
-    <t>NS: 3 18</t>
-  </si>
-  <si>
-    <t>3 9 12 18</t>
-  </si>
-  <si>
-    <t>3 12 18</t>
-  </si>
-  <si>
-    <t>TE15</t>
-  </si>
-  <si>
-    <t>Great World</t>
-  </si>
-  <si>
-    <t>TE16</t>
-  </si>
-  <si>
-    <t>Havelock</t>
-  </si>
-  <si>
-    <t>TE17  EW16  NE3</t>
-  </si>
-  <si>
-    <t>2 16</t>
-  </si>
-  <si>
-    <t>EW: 2 11 16
-NE: 12 19</t>
-  </si>
-  <si>
-    <t>5✅ 19</t>
-  </si>
-  <si>
-    <t>5 9</t>
-  </si>
-  <si>
-    <t>10 18</t>
-  </si>
-  <si>
-    <t>EW: 5 10 19
-NE: 2 9</t>
-  </si>
-  <si>
-    <t>TE18</t>
-  </si>
-  <si>
-    <t>Maxwell</t>
-  </si>
-  <si>
-    <t>GBTB: 3 18</t>
-  </si>
-  <si>
-    <t>TE19</t>
-  </si>
-  <si>
-    <t>Shenton Way</t>
-  </si>
-  <si>
-    <t>TE 20</t>
-  </si>
-  <si>
-    <t>7 9 17</t>
-  </si>
-  <si>
-    <t>NS/CC: 7
-GBTB: 9 17</t>
-  </si>
-  <si>
-    <t>9 10</t>
-  </si>
-  <si>
-    <t>NS/CC: 3 17
-WN: 8 16</t>
-  </si>
-  <si>
-    <t>TE22</t>
-  </si>
-  <si>
-    <t>GBTB/Marina Barrage: 9</t>
-  </si>
-</sst>
+Jewel: 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS1  EW24  JE5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bukit Batok</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Marina South Pier</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bukit Gombak</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:color rgb="FF000000"/>
+      </ns0:rPr>
+      <ns0:t xml:space="preserve">NS3A </ns0:t>
+    </ns0:r>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:color rgb="FF000000"/>
+        <ns0:u/>
+      </ns0:rPr>
+      <ns0:t>Infill station</ns0:t>
+    </ns0:r>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Brickland</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS4  BP1  JS1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Choa Chu Kang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Yew Tee</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kranji</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Marsiling</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS9  TE2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Woodlands</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE: 23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE: 2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Admiralty</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sembawang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Canberra</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Yishun</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Khatib</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Yio Chu Kang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS16  CR11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Ang Mo Kio</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS17  CC15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bishan</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 9 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 9 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 11 16 22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Braddell</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Toa Payoh</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Novena</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS21 – DT11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Newton</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS22  TE14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Orchard</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE: 14 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12 15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE: 4 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Somerset</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 12 15 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 10 13 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS24  NE6  CC1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dhoby Ghaut</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 11 14 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 8 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS25  EW13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>13 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 13 16 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Thus Link/Marina South Pier: 9 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Thus Link/Jurong East: 9 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS26  EW14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PR/MSP: 9 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS27  CE2  TE20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Marina Bay</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS28</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 13 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE1  CC29</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>HarbourFront</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Harbourfront</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE3  EW16  TE17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11 13 19✅</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:r>
+      <ns0:t xml:space="preserve">11 </ns0:t>
+    </ns0:r>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:b/>
+        <ns0:color theme="1"/>
+      </ns0:rPr>
+      <ns0:t>13</ns0:t>
+    </ns0:r>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:color theme="1"/>
+      </ns0:rPr>
+      <ns0:t xml:space="preserve"> 19</ns0:t>
+    </ns0:r>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 13
+TE: 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Punggol</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>12 14 19✅</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 12 14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 12
+TE: 6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE4  DT19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Chinatown</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 12 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 10 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Clarke Quay</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 11 14 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE6  NS24  CC1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 16 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 13 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 9 21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE7  DT12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Little India</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Farrer Park</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>City Square: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>City Square: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Boon Keng</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Potong Pasir</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Woodleigh</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE12  CC13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Serangoon</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 19 29</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 6 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kovan</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Heartland Mall: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hertland Mall: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE14  CR8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hougang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hougang Mall: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hougang Mall: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Buangkok</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 16 24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE16  STC</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sengkang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 11 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 14 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE17  PTC  CP4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 14 23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC1  NS24  NE6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Marina Bay / Dhoby Ghaut</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bras Basah</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Esplanade</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC4  DT15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Promenade</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 10 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>HF: 9
+DT: 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DG/MSP: 8
+DT: 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Nicoll Highway</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Stadium</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kallang Leisure Park: 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kallang Leisure Park: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Mountbatten</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Dakota</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC9  EW8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC10  DT26</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MacPherson</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 5 8 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BP: 1
+Expo: 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BP: 12
+Expo: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tai Seng</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bartley</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC13  NE12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 1
+Nex: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 12
+Nex: 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC14</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Lorong Chuan</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC15  NS17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Marymount</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC17  TE9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Caldecott</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE: 6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE: 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC18  Infill station</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bukit Brown</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC19  DT9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Botanic Gardens</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT: 5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Farrer Road</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Holland Village</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC22  EW21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 8✅(出口)</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5✅ 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>one-north</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t xml:space="preserve"> 1 5 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 8 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kent Ridge</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Haw Par Villa</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC26</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Pasir Panjang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC27</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Labrador Park</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC28</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Telok Blangah</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC29  NE1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CE1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bayfront</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 10 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DG/MSP: 5
+MBS: 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MSP: 4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CE2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT1 – BP6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bukit Panjang</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Cashew</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hillview</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:color rgb="FF000000"/>
+      </ns0:rPr>
+      <ns0:t xml:space="preserve">DT4 </ns0:t>
+    </ns0:r>
+    <ns0:r>
+      <ns0:rPr>
+        <ns0:rFont val="Arial"/>
+        <ns0:color rgb="FF000000"/>
+        <ns0:u/>
+      </ns0:rPr>
+      <ns0:t>Infill station</ns0:t>
+    </ns0:r>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hume</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Beauty World</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT6  CR15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>King Albert Park</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Sixth Avenue</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tan Kah Kee</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT9  CC19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT10  TE11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Stevens</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT11 – NS21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT12  NE7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Rochor</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT14  EW12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT15  CC4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT16  CE1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Expo/MBS: 4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BP/HF: 5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Downtown</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Telok Ayer</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT19  NE4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 9 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 9 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 4 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NE: 1 4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Fort Canning</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT21</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bencoolen</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Jalan Besar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bendemeer</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT24</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Geylang Bahru</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT25</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Mattar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT26  CC10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Expo: 1
+CC: 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BP: 12
+CC: 3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT27</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Ubi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT28</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kaki Bukit</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT29</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bedok North</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT30</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bedok Reservoir</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT31</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tampines West</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT32 – EW2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT33</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Tampines East</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT34</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Upper Changi</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DT35  CG1</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE1 – RTS</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Woodlands North</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 12 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE2  NS9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 12 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Gardens by the Bay</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 9 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>6 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Woodlands South</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Springleaf</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>8 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 11</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE5</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Lentor</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE6</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Mayflower</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE7  CR13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bright Hill</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 8 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 13 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>11 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE8</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Upper Thomson</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE9  CC17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 2</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>CC: 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE11  DT10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 13 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 7 13 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BP: 13
+Expo: 4</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 8 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>15 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>4 8 14 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>BP: 8
+Expo: 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Napier</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>1 8 13 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>GBTB: 8 13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 9 12 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>WN: 9 12</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE13</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Orchard Boulevard</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE14  NS22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3(NS→Exit 1) 9 12 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 9 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS: 3 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 9 12 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>3 12 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE15</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Great World</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Havelock</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE17  EW16  NE3</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>2 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 2 11 16
+NE: 12 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5✅ 19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>5 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>10 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>EW: 5 10 19
+NE: 2 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Maxwell</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>GBTB: 3 18</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE19</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Shenton Way</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE 20</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>7 9 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS/CC: 7
+GBTB: 9 17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>9 10</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NS/CC: 3 17
+WN: 8 16</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TE22</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>GBTB/Marina Barrage: 9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bayshore</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Punggol Coast</ns0:t>
+  </ns0:si>
+</ns0:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11010,670 +11016,670 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.75"/>
-    <col customWidth="1" min="2" max="2" width="10.88"/>
-    <col customWidth="1" min="3" max="3" width="10.38"/>
-    <col customWidth="1" min="4" max="4" width="10.5"/>
-    <col customWidth="1" min="5" max="5" width="5.63"/>
-    <col customWidth="1" min="6" max="6" width="8.75"/>
-    <col customWidth="1" min="7" max="7" width="14.5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="42"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>255</v>
-      </c>
-      <c r="J3" s="43"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>258</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>263</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="G7" s="42"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="G8" s="44"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="G9" s="42"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D13" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D15" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="G15" s="42"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="G16" s="44"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="G17" s="42"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D18" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="G18" s="44"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D19" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="G20" s="44"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D26" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="44" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>304</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="42"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D28" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="E28" s="44" t="s">
-        <v>216</v>
-      </c>
-      <c r="F28" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="G28" s="44"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>307</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="42"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="D30" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="F30" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="44"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E31" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G31" s="44"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="B2"/>
-    <hyperlink r:id="rId2" ref="B3"/>
-    <hyperlink r:id="rId3" ref="B5"/>
-    <hyperlink r:id="rId4" ref="B7"/>
-    <hyperlink r:id="rId5" ref="B9"/>
-    <hyperlink r:id="rId6" ref="B11"/>
-    <hyperlink r:id="rId7" ref="B13"/>
-    <hyperlink r:id="rId8" ref="B15"/>
-    <hyperlink r:id="rId9" ref="B17"/>
-    <hyperlink r:id="rId10" ref="B19"/>
-    <hyperlink r:id="rId11" ref="B21"/>
-    <hyperlink r:id="rId12" ref="B23"/>
-    <hyperlink r:id="rId13" ref="B25"/>
-    <hyperlink r:id="rId14" ref="B27"/>
-    <hyperlink r:id="rId15" ref="B29"/>
-    <hyperlink r:id="rId16" ref="B31"/>
-  </hyperlinks>
-  <drawing r:id="rId17"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="0" summaryRight="0"/>
+  </ns0:sheetPr>
+  <ns0:sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <ns0:cols>
+    <ns0:col customWidth="1" min="1" max="1" width="4.75"/>
+    <ns0:col customWidth="1" min="2" max="2" width="10.88"/>
+    <ns0:col customWidth="1" min="3" max="3" width="10.38"/>
+    <ns0:col customWidth="1" min="4" max="4" width="10.5"/>
+    <ns0:col customWidth="1" min="5" max="5" width="5.63"/>
+    <ns0:col customWidth="1" min="6" max="6" width="8.75"/>
+    <ns0:col customWidth="1" min="7" max="7" width="14.5"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="41" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="41" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="41" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="41" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="41" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="41" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="41" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="4" t="s">
+        <ns0:v>249</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="17" t="s">
+        <ns0:v>250</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="42" t="s">
+        <ns0:v>112</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="42" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="42" t="s">
+        <ns0:v>112</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="42"/>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="4" t="s">
+        <ns0:v>252</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="17" t="s">
+        <ns0:v>79</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="5" t="s">
+        <ns0:v>253</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="42" t="s">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="5" t="s">
+        <ns0:v>254</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="42" t="s">
+        <ns0:v>255</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" s="43"/>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="4"/>
+      <ns0:c r="B4" s="4"/>
+      <ns0:c r="C4" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="9" t="s">
+        <ns0:v>257</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="44" t="s">
+        <ns0:v>194</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="44" t="s">
+        <ns0:v>258</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" s="44" t="s">
+        <ns0:v>259</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="4" t="s">
+        <ns0:v>260</ns0:v>
+      </ns0:c>
+      <ns0:c r="B5" s="17" t="s">
+        <ns0:v>261</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="42" t="s">
+        <ns0:v>262</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="42" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5" s="42" t="s">
+        <ns0:v>263</ns0:v>
+      </ns0:c>
+      <ns0:c r="G5" s="42" t="s">
+        <ns0:v>264</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="4"/>
+      <ns0:c r="B6" s="4"/>
+      <ns0:c r="C6" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="9" t="s">
+        <ns0:v>265</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="44" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="44" t="s">
+        <ns0:v>263</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" s="44" t="s">
+        <ns0:v>264</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="4" t="s">
+        <ns0:v>266</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" s="17" t="s">
+        <ns0:v>267</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="42" t="s">
+        <ns0:v>268</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="42" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="42" t="s">
+        <ns0:v>268</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="42"/>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" s="4"/>
+      <ns0:c r="B8" s="4"/>
+      <ns0:c r="C8" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="44" t="s">
+        <ns0:v>268</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="44" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="44" t="s">
+        <ns0:v>268</ns0:v>
+      </ns0:c>
+      <ns0:c r="G8" s="44"/>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" s="4" t="s">
+        <ns0:v>269</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9" s="17" t="s">
+        <ns0:v>233</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="42" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="42" t="s">
+        <ns0:v>105</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="42" t="s">
+        <ns0:v>270</ns0:v>
+      </ns0:c>
+      <ns0:c r="G9" s="42"/>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="4"/>
+      <ns0:c r="B10" s="4"/>
+      <ns0:c r="C10" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="44" t="s">
+        <ns0:v>271</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="44" t="s">
+        <ns0:v>108</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="44" t="s">
+        <ns0:v>272</ns0:v>
+      </ns0:c>
+      <ns0:c r="G10" s="9" t="s">
+        <ns0:v>273</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" s="4" t="s">
+        <ns0:v>274</ns0:v>
+      </ns0:c>
+      <ns0:c r="B11" s="17" t="s">
+        <ns0:v>275</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" s="42" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F11" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G11" s="42" t="s">
+        <ns0:v>276</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" s="4"/>
+      <ns0:c r="B12" s="4"/>
+      <ns0:c r="C12" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D12" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" s="44" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F12" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G12" s="44" t="s">
+        <ns0:v>277</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" s="4" t="s">
+        <ns0:v>278</ns0:v>
+      </ns0:c>
+      <ns0:c r="B13" s="17" t="s">
+        <ns0:v>279</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D13" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" s="42" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F13" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G13" s="42" t="s">
+        <ns0:v>280</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" s="4"/>
+      <ns0:c r="B14" s="4"/>
+      <ns0:c r="C14" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D14" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" s="44" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F14" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G14" s="44" t="s">
+        <ns0:v>281</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" s="4" t="s">
+        <ns0:v>282</ns0:v>
+      </ns0:c>
+      <ns0:c r="B15" s="17" t="s">
+        <ns0:v>283</ns0:v>
+      </ns0:c>
+      <ns0:c r="C15" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D15" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E15" s="42" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F15" s="42" t="s">
+        <ns0:v>194</ns0:v>
+      </ns0:c>
+      <ns0:c r="G15" s="42"/>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" s="4"/>
+      <ns0:c r="B16" s="4"/>
+      <ns0:c r="C16" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D16" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" s="44" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F16" s="44" t="s">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="G16" s="44"/>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" s="4" t="s">
+        <ns0:v>284</ns0:v>
+      </ns0:c>
+      <ns0:c r="B17" s="17" t="s">
+        <ns0:v>285</ns0:v>
+      </ns0:c>
+      <ns0:c r="C17" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D17" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E17" s="42" t="s">
+        <ns0:v>54</ns0:v>
+      </ns0:c>
+      <ns0:c r="F17" s="42" t="s">
+        <ns0:v>194</ns0:v>
+      </ns0:c>
+      <ns0:c r="G17" s="42"/>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" s="4"/>
+      <ns0:c r="B18" s="4"/>
+      <ns0:c r="C18" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D18" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E18" s="44" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="F18" s="44" t="s">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="G18" s="44"/>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" s="4" t="s">
+        <ns0:v>286</ns0:v>
+      </ns0:c>
+      <ns0:c r="B19" s="17" t="s">
+        <ns0:v>287</ns0:v>
+      </ns0:c>
+      <ns0:c r="C19" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D19" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E19" s="42" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F19" s="42" t="s">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="G19" s="42"/>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" s="4"/>
+      <ns0:c r="B20" s="4"/>
+      <ns0:c r="C20" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D20" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E20" s="44" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F20" s="44" t="s">
+        <ns0:v>194</ns0:v>
+      </ns0:c>
+      <ns0:c r="G20" s="44"/>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="A21" s="4" t="s">
+        <ns0:v>288</ns0:v>
+      </ns0:c>
+      <ns0:c r="B21" s="17" t="s">
+        <ns0:v>289</ns0:v>
+      </ns0:c>
+      <ns0:c r="C21" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D21" s="42" t="s">
+        <ns0:v>112</ns0:v>
+      </ns0:c>
+      <ns0:c r="E21" s="42" t="s">
+        <ns0:v>94</ns0:v>
+      </ns0:c>
+      <ns0:c r="F21" s="42" t="s">
+        <ns0:v>290</ns0:v>
+      </ns0:c>
+      <ns0:c r="G21" s="42" t="s">
+        <ns0:v>291</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" s="4"/>
+      <ns0:c r="B22" s="4"/>
+      <ns0:c r="C22" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D22" s="44" t="s">
+        <ns0:v>111</ns0:v>
+      </ns0:c>
+      <ns0:c r="E22" s="44" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="F22" s="44" t="s">
+        <ns0:v>292</ns0:v>
+      </ns0:c>
+      <ns0:c r="G22" s="44" t="s">
+        <ns0:v>293</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" s="4" t="s">
+        <ns0:v>294</ns0:v>
+      </ns0:c>
+      <ns0:c r="B23" s="17" t="s">
+        <ns0:v>295</ns0:v>
+      </ns0:c>
+      <ns0:c r="C23" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D23" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E23" s="42" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F23" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G23" s="42" t="s">
+        <ns0:v>296</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" s="4"/>
+      <ns0:c r="B24" s="4"/>
+      <ns0:c r="C24" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D24" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E24" s="44" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F24" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G24" s="44" t="s">
+        <ns0:v>297</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" s="4" t="s">
+        <ns0:v>298</ns0:v>
+      </ns0:c>
+      <ns0:c r="B25" s="17" t="s">
+        <ns0:v>299</ns0:v>
+      </ns0:c>
+      <ns0:c r="C25" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D25" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E25" s="42" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F25" s="42" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G25" s="42" t="s">
+        <ns0:v>300</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" s="4"/>
+      <ns0:c r="B26" s="4"/>
+      <ns0:c r="C26" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D26" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="E26" s="44" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="F26" s="44" t="s">
+        <ns0:v>134</ns0:v>
+      </ns0:c>
+      <ns0:c r="G26" s="44" t="s">
+        <ns0:v>301</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" s="4" t="s">
+        <ns0:v>302</ns0:v>
+      </ns0:c>
+      <ns0:c r="B27" s="17" t="s">
+        <ns0:v>303</ns0:v>
+      </ns0:c>
+      <ns0:c r="C27" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D27" s="42" t="s">
+        <ns0:v>304</ns0:v>
+      </ns0:c>
+      <ns0:c r="E27" s="42" t="s">
+        <ns0:v>217</ns0:v>
+      </ns0:c>
+      <ns0:c r="F27" s="42" t="s">
+        <ns0:v>127</ns0:v>
+      </ns0:c>
+      <ns0:c r="G27" s="42"/>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" s="4"/>
+      <ns0:c r="B28" s="4"/>
+      <ns0:c r="C28" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D28" s="44" t="s">
+        <ns0:v>304</ns0:v>
+      </ns0:c>
+      <ns0:c r="E28" s="44" t="s">
+        <ns0:v>216</ns0:v>
+      </ns0:c>
+      <ns0:c r="F28" s="44" t="s">
+        <ns0:v>125</ns0:v>
+      </ns0:c>
+      <ns0:c r="G28" s="44"/>
+    </ns0:row>
+    <ns0:row r="29">
+      <ns0:c r="A29" s="4" t="s">
+        <ns0:v>305</ns0:v>
+      </ns0:c>
+      <ns0:c r="B29" s="17" t="s">
+        <ns0:v>306</ns0:v>
+      </ns0:c>
+      <ns0:c r="C29" s="42" t="s">
+        <ns0:v>251</ns0:v>
+      </ns0:c>
+      <ns0:c r="D29" s="42" t="s">
+        <ns0:v>307</ns0:v>
+      </ns0:c>
+      <ns0:c r="E29" s="42" t="s">
+        <ns0:v>195</ns0:v>
+      </ns0:c>
+      <ns0:c r="F29" s="42" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="G29" s="42"/>
+    </ns0:row>
+    <ns0:row r="30">
+      <ns0:c r="A30" s="4"/>
+      <ns0:c r="B30" s="4"/>
+      <ns0:c r="C30" s="44" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D30" s="44" t="s">
+        <ns0:v>308</ns0:v>
+      </ns0:c>
+      <ns0:c r="E30" s="44" t="s">
+        <ns0:v>194</ns0:v>
+      </ns0:c>
+      <ns0:c r="F30" s="44" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="G30" s="44"/>
+    </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" s="4" t="s">
+        <ns0:v>309</ns0:v>
+      </ns0:c>
+      <ns0:c r="B31" s="17" t="s">
+        <ns0:v>256</ns0:v>
+      </ns0:c>
+      <ns0:c r="C31" s="9" t="s">
+        <ns0:v>577</ns0:v>
+      </ns0:c>
+      <ns0:c r="D31" s="9" t="s">
+        <ns0:v>310</ns0:v>
+      </ns0:c>
+      <ns0:c r="E31" s="45" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="F31" s="9" t="s">
+        <ns0:v>310</ns0:v>
+      </ns0:c>
+      <ns0:c r="G31" s="44"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:hyperlinks>
+    <ns0:hyperlink ns1:id="rId1" ref="B2"/>
+    <ns0:hyperlink ns1:id="rId2" ref="B3"/>
+    <ns0:hyperlink ns1:id="rId3" ref="B5"/>
+    <ns0:hyperlink ns1:id="rId4" ref="B7"/>
+    <ns0:hyperlink ns1:id="rId5" ref="B9"/>
+    <ns0:hyperlink ns1:id="rId6" ref="B11"/>
+    <ns0:hyperlink ns1:id="rId7" ref="B13"/>
+    <ns0:hyperlink ns1:id="rId8" ref="B15"/>
+    <ns0:hyperlink ns1:id="rId9" ref="B17"/>
+    <ns0:hyperlink ns1:id="rId10" ref="B19"/>
+    <ns0:hyperlink ns1:id="rId11" ref="B21"/>
+    <ns0:hyperlink ns1:id="rId12" ref="B23"/>
+    <ns0:hyperlink ns1:id="rId13" ref="B25"/>
+    <ns0:hyperlink ns1:id="rId14" ref="B27"/>
+    <ns0:hyperlink ns1:id="rId15" ref="B29"/>
+    <ns0:hyperlink ns1:id="rId16" ref="B31"/>
+  </ns0:hyperlinks>
+  <ns0:drawing ns1:id="rId17"/>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20079,865 +20085,865 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.88"/>
-    <col customWidth="1" min="2" max="2" width="12.38"/>
-    <col customWidth="1" min="3" max="3" width="15.75"/>
-    <col customWidth="1" min="7" max="7" width="19.38"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="59" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="31" t="s">
-        <v>497</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>498</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>499</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>501</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>501</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>502</v>
-      </c>
-      <c r="H3" s="21"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="31"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>504</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>505</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>504</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>506</v>
-      </c>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="60" t="s">
-        <v>507</v>
-      </c>
-      <c r="B5" s="61" t="s">
-        <v>508</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="21"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="G6" s="39"/>
-      <c r="H6" s="21"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="60" t="s">
-        <v>510</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>511</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>512</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="21"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="62"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>512</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="21"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="s">
-        <v>514</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>515</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>512</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>512</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="G10" s="39"/>
-      <c r="H10" s="21"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="s">
-        <v>516</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>517</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="G11" s="35"/>
-      <c r="H11" s="21"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="31"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="G12" s="39"/>
-      <c r="H12" s="21"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="s">
-        <v>518</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>519</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>520</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>521</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>512</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="21"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="31"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>522</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>523</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>524</v>
-      </c>
-      <c r="G14" s="39"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="s">
-        <v>525</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>526</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>512</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="21"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="31"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>512</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="G16" s="39"/>
-      <c r="H16" s="21"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="s">
-        <v>527</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>528</v>
-      </c>
-      <c r="H17" s="21"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="31"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="G18" s="38" t="s">
-        <v>529</v>
-      </c>
-      <c r="H18" s="21"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="31" t="s">
-        <v>530</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>427</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>531</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>454</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>532</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>533</v>
-      </c>
-      <c r="H19" s="21"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="31"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>534</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>535</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>536</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>537</v>
-      </c>
-      <c r="H20" s="21"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="s">
-        <v>538</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>539</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>540</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>541</v>
-      </c>
-      <c r="H21" s="21"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="31"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>542</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>543</v>
-      </c>
-      <c r="H22" s="21"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="s">
-        <v>544</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>545</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="G23" s="35"/>
-      <c r="H23" s="21"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="31"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>546</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>546</v>
-      </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="21"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="s">
-        <v>547</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D25" s="34" t="s">
-        <v>548</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>550</v>
-      </c>
-      <c r="H25" s="21"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="31"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>551</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>552</v>
-      </c>
-      <c r="G26" s="38" t="s">
-        <v>550</v>
-      </c>
-      <c r="H26" s="21"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>554</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="G27" s="35"/>
-      <c r="H27" s="21"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="31"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>546</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>546</v>
-      </c>
-      <c r="G28" s="39"/>
-      <c r="H28" s="21"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="31" t="s">
-        <v>555</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>556</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>513</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="G29" s="35"/>
-      <c r="H29" s="21"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="31"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>546</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>546</v>
-      </c>
-      <c r="G30" s="39"/>
-      <c r="H30" s="21"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D31" s="34" t="s">
-        <v>558</v>
-      </c>
-      <c r="E31" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="34" t="s">
-        <v>320</v>
-      </c>
-      <c r="G31" s="34" t="s">
-        <v>559</v>
-      </c>
-      <c r="H31" s="21"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="31"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>560</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>561</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>562</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>563</v>
-      </c>
-      <c r="H32" s="21"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="s">
-        <v>564</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>565</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="E33" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34" t="s">
-        <v>566</v>
-      </c>
-      <c r="H33" s="21"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="31"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>543</v>
-      </c>
-      <c r="H34" s="21"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="31" t="s">
-        <v>567</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>568</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="21"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="63"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="21"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="63" t="s">
-        <v>569</v>
-      </c>
-      <c r="B37" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>498</v>
-      </c>
-      <c r="D37" s="34" t="s">
-        <v>570</v>
-      </c>
-      <c r="E37" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="F37" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>571</v>
-      </c>
-      <c r="H37" s="21"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="31"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>572</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="G38" s="38" t="s">
-        <v>573</v>
-      </c>
-      <c r="H38" s="21"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="31" t="s">
-        <v>574</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>503</v>
-      </c>
-      <c r="C39" s="64" t="s">
-        <v>503</v>
-      </c>
-      <c r="D39" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="F39" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39" s="38" t="s">
-        <v>575</v>
-      </c>
-      <c r="H39" s="21"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="65"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="B2"/>
-    <hyperlink r:id="rId2" ref="B3"/>
-    <hyperlink r:id="rId3" ref="B5"/>
-    <hyperlink r:id="rId4" ref="B7"/>
-    <hyperlink r:id="rId5" ref="B9"/>
-    <hyperlink r:id="rId6" ref="B11"/>
-    <hyperlink r:id="rId7" ref="B13"/>
-    <hyperlink r:id="rId8" ref="B15"/>
-    <hyperlink r:id="rId9" ref="B17"/>
-    <hyperlink r:id="rId10" ref="B19"/>
-    <hyperlink r:id="rId11" ref="B21"/>
-    <hyperlink r:id="rId12" ref="B23"/>
-    <hyperlink r:id="rId13" ref="B25"/>
-    <hyperlink r:id="rId14" ref="B27"/>
-    <hyperlink r:id="rId15" ref="B29"/>
-    <hyperlink r:id="rId16" ref="B31"/>
-    <hyperlink r:id="rId17" ref="B33"/>
-    <hyperlink r:id="rId18" ref="B35"/>
-    <hyperlink r:id="rId19" ref="B37"/>
-    <hyperlink r:id="rId20" ref="B39"/>
-  </hyperlinks>
-  <drawing r:id="rId21"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="0" summaryRight="0"/>
+  </ns0:sheetPr>
+  <ns0:sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <ns0:cols>
+    <ns0:col customWidth="1" min="1" max="1" width="4.88"/>
+    <ns0:col customWidth="1" min="2" max="2" width="12.38"/>
+    <ns0:col customWidth="1" min="3" max="3" width="15.75"/>
+    <ns0:col customWidth="1" min="7" max="7" width="19.38"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="59" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="59" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="59" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="59" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="59" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="59" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="59" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="31" t="s">
+        <ns0:v>497</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="32" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="34" t="s">
+        <ns0:v>499</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="34" t="s">
+        <ns0:v>217</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="34" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="35"/>
+      <ns0:c r="H2" s="21"/>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="31" t="s">
+        <ns0:v>500</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="32" t="s">
+        <ns0:v>183</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="34" t="s">
+        <ns0:v>501</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="34" t="s">
+        <ns0:v>94</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="34" t="s">
+        <ns0:v>501</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="34" t="s">
+        <ns0:v>502</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="21"/>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="31"/>
+      <ns0:c r="B4" s="36"/>
+      <ns0:c r="C4" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="38" t="s">
+        <ns0:v>504</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="38" t="s">
+        <ns0:v>505</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="38" t="s">
+        <ns0:v>504</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" s="38" t="s">
+        <ns0:v>506</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4" s="21"/>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="60" t="s">
+        <ns0:v>507</ns0:v>
+      </ns0:c>
+      <ns0:c r="B5" s="61" t="s">
+        <ns0:v>508</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="34" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G5" s="35"/>
+      <ns0:c r="H5" s="21"/>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="62"/>
+      <ns0:c r="B6" s="62"/>
+      <ns0:c r="C6" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="38" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" s="39"/>
+      <ns0:c r="H6" s="21"/>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="60" t="s">
+        <ns0:v>510</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" s="61" t="s">
+        <ns0:v>511</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="34" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="35"/>
+      <ns0:c r="H7" s="21"/>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" s="62"/>
+      <ns0:c r="B8" s="62"/>
+      <ns0:c r="C8" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="38" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G8" s="39"/>
+      <ns0:c r="H8" s="21"/>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" s="31" t="s">
+        <ns0:v>514</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9" s="32" t="s">
+        <ns0:v>515</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="34" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G9" s="35"/>
+      <ns0:c r="H9" s="21"/>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="31"/>
+      <ns0:c r="B10" s="36"/>
+      <ns0:c r="C10" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="38" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G10" s="39"/>
+      <ns0:c r="H10" s="21"/>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" s="31" t="s">
+        <ns0:v>516</ns0:v>
+      </ns0:c>
+      <ns0:c r="B11" s="32" t="s">
+        <ns0:v>517</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" s="34" t="s">
+        <ns0:v>126</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F11" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G11" s="35"/>
+      <ns0:c r="H11" s="21"/>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" s="31"/>
+      <ns0:c r="B12" s="36"/>
+      <ns0:c r="C12" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D12" s="38" t="s">
+        <ns0:v>126</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F12" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G12" s="39"/>
+      <ns0:c r="H12" s="21"/>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" s="31" t="s">
+        <ns0:v>518</ns0:v>
+      </ns0:c>
+      <ns0:c r="B13" s="32" t="s">
+        <ns0:v>519</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D13" s="34" t="s">
+        <ns0:v>520</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" s="34" t="s">
+        <ns0:v>521</ns0:v>
+      </ns0:c>
+      <ns0:c r="F13" s="34" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="G13" s="35"/>
+      <ns0:c r="H13" s="21"/>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" s="31"/>
+      <ns0:c r="B14" s="36"/>
+      <ns0:c r="C14" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D14" s="38" t="s">
+        <ns0:v>522</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" s="38" t="s">
+        <ns0:v>523</ns0:v>
+      </ns0:c>
+      <ns0:c r="F14" s="38" t="s">
+        <ns0:v>524</ns0:v>
+      </ns0:c>
+      <ns0:c r="G14" s="39"/>
+      <ns0:c r="H14" s="21"/>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" s="31" t="s">
+        <ns0:v>525</ns0:v>
+      </ns0:c>
+      <ns0:c r="B15" s="32" t="s">
+        <ns0:v>526</ns0:v>
+      </ns0:c>
+      <ns0:c r="C15" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D15" s="34" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="E15" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F15" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G15" s="35"/>
+      <ns0:c r="H15" s="21"/>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" s="31"/>
+      <ns0:c r="B16" s="36"/>
+      <ns0:c r="C16" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D16" s="38" t="s">
+        <ns0:v>512</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F16" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G16" s="39"/>
+      <ns0:c r="H16" s="21"/>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" s="31" t="s">
+        <ns0:v>527</ns0:v>
+      </ns0:c>
+      <ns0:c r="B17" s="32" t="s">
+        <ns0:v>365</ns0:v>
+      </ns0:c>
+      <ns0:c r="C17" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D17" s="34" t="s">
+        <ns0:v>148</ns0:v>
+      </ns0:c>
+      <ns0:c r="E17" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F17" s="34" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G17" s="34" t="s">
+        <ns0:v>528</ns0:v>
+      </ns0:c>
+      <ns0:c r="H17" s="21"/>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" s="31"/>
+      <ns0:c r="B18" s="36"/>
+      <ns0:c r="C18" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D18" s="38" t="s">
+        <ns0:v>148</ns0:v>
+      </ns0:c>
+      <ns0:c r="E18" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F18" s="38" t="s">
+        <ns0:v>509</ns0:v>
+      </ns0:c>
+      <ns0:c r="G18" s="38" t="s">
+        <ns0:v>529</ns0:v>
+      </ns0:c>
+      <ns0:c r="H18" s="21"/>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" s="31" t="s">
+        <ns0:v>530</ns0:v>
+      </ns0:c>
+      <ns0:c r="B19" s="32" t="s">
+        <ns0:v>427</ns0:v>
+      </ns0:c>
+      <ns0:c r="C19" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D19" s="34" t="s">
+        <ns0:v>531</ns0:v>
+      </ns0:c>
+      <ns0:c r="E19" s="34" t="s">
+        <ns0:v>454</ns0:v>
+      </ns0:c>
+      <ns0:c r="F19" s="34" t="s">
+        <ns0:v>532</ns0:v>
+      </ns0:c>
+      <ns0:c r="G19" s="34" t="s">
+        <ns0:v>533</ns0:v>
+      </ns0:c>
+      <ns0:c r="H19" s="21"/>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="A20" s="31"/>
+      <ns0:c r="B20" s="36"/>
+      <ns0:c r="C20" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D20" s="38" t="s">
+        <ns0:v>534</ns0:v>
+      </ns0:c>
+      <ns0:c r="E20" s="38" t="s">
+        <ns0:v>535</ns0:v>
+      </ns0:c>
+      <ns0:c r="F20" s="38" t="s">
+        <ns0:v>536</ns0:v>
+      </ns0:c>
+      <ns0:c r="G20" s="38" t="s">
+        <ns0:v>537</ns0:v>
+      </ns0:c>
+      <ns0:c r="H20" s="21"/>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="A21" s="31" t="s">
+        <ns0:v>538</ns0:v>
+      </ns0:c>
+      <ns0:c r="B21" s="32" t="s">
+        <ns0:v>539</ns0:v>
+      </ns0:c>
+      <ns0:c r="C21" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D21" s="34" t="s">
+        <ns0:v>540</ns0:v>
+      </ns0:c>
+      <ns0:c r="E21" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F21" s="34" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="G21" s="34" t="s">
+        <ns0:v>541</ns0:v>
+      </ns0:c>
+      <ns0:c r="H21" s="21"/>
+    </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" s="31"/>
+      <ns0:c r="B22" s="36"/>
+      <ns0:c r="C22" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D22" s="38" t="s">
+        <ns0:v>542</ns0:v>
+      </ns0:c>
+      <ns0:c r="E22" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F22" s="38" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="G22" s="38" t="s">
+        <ns0:v>543</ns0:v>
+      </ns0:c>
+      <ns0:c r="H22" s="21"/>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" s="31" t="s">
+        <ns0:v>544</ns0:v>
+      </ns0:c>
+      <ns0:c r="B23" s="32" t="s">
+        <ns0:v>545</ns0:v>
+      </ns0:c>
+      <ns0:c r="C23" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D23" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E23" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F23" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="G23" s="35"/>
+      <ns0:c r="H23" s="21"/>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" s="31"/>
+      <ns0:c r="B24" s="36"/>
+      <ns0:c r="C24" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D24" s="38" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E24" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F24" s="38" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="G24" s="39"/>
+      <ns0:c r="H24" s="21"/>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" s="31" t="s">
+        <ns0:v>547</ns0:v>
+      </ns0:c>
+      <ns0:c r="B25" s="32" t="s">
+        <ns0:v>223</ns0:v>
+      </ns0:c>
+      <ns0:c r="C25" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D25" s="34" t="s">
+        <ns0:v>548</ns0:v>
+      </ns0:c>
+      <ns0:c r="E25" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F25" s="34" t="s">
+        <ns0:v>549</ns0:v>
+      </ns0:c>
+      <ns0:c r="G25" s="34" t="s">
+        <ns0:v>550</ns0:v>
+      </ns0:c>
+      <ns0:c r="H25" s="21"/>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" s="31"/>
+      <ns0:c r="B26" s="36"/>
+      <ns0:c r="C26" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D26" s="38" t="s">
+        <ns0:v>551</ns0:v>
+      </ns0:c>
+      <ns0:c r="E26" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F26" s="38" t="s">
+        <ns0:v>552</ns0:v>
+      </ns0:c>
+      <ns0:c r="G26" s="38" t="s">
+        <ns0:v>550</ns0:v>
+      </ns0:c>
+      <ns0:c r="H26" s="21"/>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" s="31" t="s">
+        <ns0:v>553</ns0:v>
+      </ns0:c>
+      <ns0:c r="B27" s="32" t="s">
+        <ns0:v>554</ns0:v>
+      </ns0:c>
+      <ns0:c r="C27" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D27" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E27" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F27" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="G27" s="35"/>
+      <ns0:c r="H27" s="21"/>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" s="31"/>
+      <ns0:c r="B28" s="36"/>
+      <ns0:c r="C28" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D28" s="38" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E28" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F28" s="38" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="G28" s="39"/>
+      <ns0:c r="H28" s="21"/>
+    </ns0:row>
+    <ns0:row r="29">
+      <ns0:c r="A29" s="31" t="s">
+        <ns0:v>555</ns0:v>
+      </ns0:c>
+      <ns0:c r="B29" s="32" t="s">
+        <ns0:v>556</ns0:v>
+      </ns0:c>
+      <ns0:c r="C29" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D29" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E29" s="34" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F29" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="G29" s="35"/>
+      <ns0:c r="H29" s="21"/>
+    </ns0:row>
+    <ns0:row r="30">
+      <ns0:c r="A30" s="31"/>
+      <ns0:c r="B30" s="36"/>
+      <ns0:c r="C30" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D30" s="38" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E30" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F30" s="38" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="G30" s="39"/>
+      <ns0:c r="H30" s="21"/>
+    </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" s="31" t="s">
+        <ns0:v>557</ns0:v>
+      </ns0:c>
+      <ns0:c r="B31" s="32" t="s">
+        <ns0:v>79</ns0:v>
+      </ns0:c>
+      <ns0:c r="C31" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D31" s="34" t="s">
+        <ns0:v>558</ns0:v>
+      </ns0:c>
+      <ns0:c r="E31" s="34" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="F31" s="34" t="s">
+        <ns0:v>320</ns0:v>
+      </ns0:c>
+      <ns0:c r="G31" s="34" t="s">
+        <ns0:v>559</ns0:v>
+      </ns0:c>
+      <ns0:c r="H31" s="21"/>
+    </ns0:row>
+    <ns0:row r="32">
+      <ns0:c r="A32" s="31"/>
+      <ns0:c r="B32" s="36"/>
+      <ns0:c r="C32" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D32" s="38" t="s">
+        <ns0:v>560</ns0:v>
+      </ns0:c>
+      <ns0:c r="E32" s="38" t="s">
+        <ns0:v>561</ns0:v>
+      </ns0:c>
+      <ns0:c r="F32" s="38" t="s">
+        <ns0:v>562</ns0:v>
+      </ns0:c>
+      <ns0:c r="G32" s="38" t="s">
+        <ns0:v>563</ns0:v>
+      </ns0:c>
+      <ns0:c r="H32" s="21"/>
+    </ns0:row>
+    <ns0:row r="33">
+      <ns0:c r="A33" s="31" t="s">
+        <ns0:v>564</ns0:v>
+      </ns0:c>
+      <ns0:c r="B33" s="32" t="s">
+        <ns0:v>565</ns0:v>
+      </ns0:c>
+      <ns0:c r="C33" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D33" s="34" t="s">
+        <ns0:v>546</ns0:v>
+      </ns0:c>
+      <ns0:c r="E33" s="34" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="F33" s="34"/>
+      <ns0:c r="G33" s="34" t="s">
+        <ns0:v>566</ns0:v>
+      </ns0:c>
+      <ns0:c r="H33" s="21"/>
+    </ns0:row>
+    <ns0:row r="34">
+      <ns0:c r="A34" s="31"/>
+      <ns0:c r="B34" s="36"/>
+      <ns0:c r="C34" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D34" s="38" t="s">
+        <ns0:v>64</ns0:v>
+      </ns0:c>
+      <ns0:c r="E34" s="38" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="F34" s="38" t="s">
+        <ns0:v>240</ns0:v>
+      </ns0:c>
+      <ns0:c r="G34" s="38" t="s">
+        <ns0:v>543</ns0:v>
+      </ns0:c>
+      <ns0:c r="H34" s="21"/>
+    </ns0:row>
+    <ns0:row r="35">
+      <ns0:c r="A35" s="31" t="s">
+        <ns0:v>567</ns0:v>
+      </ns0:c>
+      <ns0:c r="B35" s="32" t="s">
+        <ns0:v>568</ns0:v>
+      </ns0:c>
+      <ns0:c r="C35" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D35" s="34" t="s">
+        <ns0:v>126</ns0:v>
+      </ns0:c>
+      <ns0:c r="E35" s="34" t="s">
+        <ns0:v>126</ns0:v>
+      </ns0:c>
+      <ns0:c r="F35" s="35"/>
+      <ns0:c r="G35" s="35"/>
+      <ns0:c r="H35" s="21"/>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" s="63"/>
+      <ns0:c r="B36" s="36"/>
+      <ns0:c r="C36" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D36" s="38" t="s">
+        <ns0:v>126</ns0:v>
+      </ns0:c>
+      <ns0:c r="E36" s="38" t="s">
+        <ns0:v>126</ns0:v>
+      </ns0:c>
+      <ns0:c r="F36" s="39"/>
+      <ns0:c r="G36" s="39"/>
+      <ns0:c r="H36" s="21"/>
+    </ns0:row>
+    <ns0:row r="37">
+      <ns0:c r="A37" s="63" t="s">
+        <ns0:v>569</ns0:v>
+      </ns0:c>
+      <ns0:c r="B37" s="32" t="s">
+        <ns0:v>246</ns0:v>
+      </ns0:c>
+      <ns0:c r="C37" s="33" t="s">
+        <ns0:v>498</ns0:v>
+      </ns0:c>
+      <ns0:c r="D37" s="34" t="s">
+        <ns0:v>570</ns0:v>
+      </ns0:c>
+      <ns0:c r="E37" s="34" t="s">
+        <ns0:v>125</ns0:v>
+      </ns0:c>
+      <ns0:c r="F37" s="34" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="G37" s="34" t="s">
+        <ns0:v>571</ns0:v>
+      </ns0:c>
+      <ns0:c r="H37" s="21"/>
+    </ns0:row>
+    <ns0:row r="38">
+      <ns0:c r="A38" s="31"/>
+      <ns0:c r="B38" s="36"/>
+      <ns0:c r="C38" s="37" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D38" s="38" t="s">
+        <ns0:v>572</ns0:v>
+      </ns0:c>
+      <ns0:c r="E38" s="38" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="F38" s="38" t="s">
+        <ns0:v>317</ns0:v>
+      </ns0:c>
+      <ns0:c r="G38" s="38" t="s">
+        <ns0:v>573</ns0:v>
+      </ns0:c>
+      <ns0:c r="H38" s="21"/>
+    </ns0:row>
+    <ns0:row r="39">
+      <ns0:c r="A39" s="31" t="s">
+        <ns0:v>574</ns0:v>
+      </ns0:c>
+      <ns0:c r="B39" s="32" t="s">
+        <ns0:v>503</ns0:v>
+      </ns0:c>
+      <ns0:c r="C39" s="64" t="s">
+        <ns0:v>576</ns0:v>
+      </ns0:c>
+      <ns0:c r="D39" s="38" t="s">
+        <ns0:v>64</ns0:v>
+      </ns0:c>
+      <ns0:c r="E39" s="38" t="s">
+        <ns0:v>513</ns0:v>
+      </ns0:c>
+      <ns0:c r="F39" s="38" t="s">
+        <ns0:v>64</ns0:v>
+      </ns0:c>
+      <ns0:c r="G39" s="38" t="s">
+        <ns0:v>575</ns0:v>
+      </ns0:c>
+      <ns0:c r="H39" s="21"/>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" s="65"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:mergeCells count="4">
+    <ns0:mergeCell ref="A5:A6"/>
+    <ns0:mergeCell ref="B5:B6"/>
+    <ns0:mergeCell ref="A7:A8"/>
+    <ns0:mergeCell ref="B7:B8"/>
+  </ns0:mergeCells>
+  <ns0:hyperlinks>
+    <ns0:hyperlink ns1:id="rId1" ref="B2"/>
+    <ns0:hyperlink ns1:id="rId2" ref="B3"/>
+    <ns0:hyperlink ns1:id="rId3" ref="B5"/>
+    <ns0:hyperlink ns1:id="rId4" ref="B7"/>
+    <ns0:hyperlink ns1:id="rId5" ref="B9"/>
+    <ns0:hyperlink ns1:id="rId6" ref="B11"/>
+    <ns0:hyperlink ns1:id="rId7" ref="B13"/>
+    <ns0:hyperlink ns1:id="rId8" ref="B15"/>
+    <ns0:hyperlink ns1:id="rId9" ref="B17"/>
+    <ns0:hyperlink ns1:id="rId10" ref="B19"/>
+    <ns0:hyperlink ns1:id="rId11" ref="B21"/>
+    <ns0:hyperlink ns1:id="rId12" ref="B23"/>
+    <ns0:hyperlink ns1:id="rId13" ref="B25"/>
+    <ns0:hyperlink ns1:id="rId14" ref="B27"/>
+    <ns0:hyperlink ns1:id="rId15" ref="B29"/>
+    <ns0:hyperlink ns1:id="rId16" ref="B31"/>
+    <ns0:hyperlink ns1:id="rId17" ref="B33"/>
+    <ns0:hyperlink ns1:id="rId18" ref="B35"/>
+    <ns0:hyperlink ns1:id="rId19" ref="B37"/>
+    <ns0:hyperlink ns1:id="rId20" ref="B39"/>
+  </ns0:hyperlinks>
+  <ns0:drawing ns1:id="rId21"/>
+</ns0:worksheet>
 </file>